--- a/Sipri_Datas.xlsx
+++ b/Sipri_Datas.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C62ACEE4-7EB6-4F60-82C5-7440496B9632}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4305" yWindow="4020" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4305" yWindow="4020" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_Datas" sheetId="2" r:id="rId1"/>
